--- a/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Buff.xlsx
+++ b/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Buff.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>##var</t>
   </si>
@@ -50,6 +50,9 @@
     <t>RemoveAction</t>
   </si>
   <si>
+    <t>OwnerEffect</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -69,6 +72,9 @@
   </si>
   <si>
     <t>Tick间隔时间</t>
+  </si>
+  <si>
+    <t>Buff自身特效</t>
   </si>
 </sst>
 </file>
@@ -1027,8 +1033,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelRow="3" outlineLevelCol="6"/>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelRow="3" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2" customWidth="1"/>
     <col min="2" max="2" width="15.875" style="2" customWidth="1"/>
@@ -1037,10 +1043,11 @@
     <col min="5" max="5" width="18.625" style="2" customWidth="1"/>
     <col min="6" max="6" width="22.25" style="2" customWidth="1"/>
     <col min="7" max="7" width="22.625" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2"/>
+    <col min="8" max="8" width="22.25" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:7">
+    <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1062,55 +1069,77 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:7">
+    <row r="2" s="1" customFormat="1" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:7">
+    <row r="3" s="1" customFormat="1" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="2:2">
+    <row r="4" s="2" customFormat="1" spans="2:8">
       <c r="B4" s="3">
+        <v>2001</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1002</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="G4" s="2">
+        <v>1002</v>
+      </c>
+      <c r="H4" s="2">
         <v>1</v>
       </c>
     </row>

--- a/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Buff.xlsx
+++ b/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Buff.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="21600"/>
   </bookViews>
   <sheets>
     <sheet name="Buff" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
   <si>
     <t>##var</t>
   </si>
@@ -35,10 +35,16 @@
     <t>Id</t>
   </si>
   <si>
+    <t>#Desc</t>
+  </si>
+  <si>
     <t>TotalTime</t>
   </si>
   <si>
-    <t>Addaction</t>
+    <t>AddAction</t>
+  </si>
+  <si>
+    <t>AddActionParam</t>
   </si>
   <si>
     <t>TickTime</t>
@@ -47,10 +53,13 @@
     <t>TickAction</t>
   </si>
   <si>
+    <t>TickActionParam</t>
+  </si>
+  <si>
     <t>RemoveAction</t>
   </si>
   <si>
-    <t>OwnerEffect</t>
+    <t>RemoveActionParam</t>
   </si>
   <si>
     <t>##type</t>
@@ -59,22 +68,37 @@
     <t>int</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>(list#sep=,),int</t>
   </si>
   <si>
+    <t>(list#sep=,),long</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
+    <t>描述</t>
+  </si>
+  <si>
     <t>总时长</t>
   </si>
   <si>
     <t>效果</t>
   </si>
   <si>
+    <t>效果参数</t>
+  </si>
+  <si>
     <t>Tick间隔时间</t>
   </si>
   <si>
-    <t>Buff自身特效</t>
+    <t>灼烧</t>
   </si>
 </sst>
 </file>
@@ -709,8 +733,12 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1033,21 +1061,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelRow="3" outlineLevelCol="7"/>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="15.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.75" style="2" customWidth="1"/>
-    <col min="4" max="4" width="22.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="22.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="22.625" style="2" customWidth="1"/>
+    <col min="2" max="3" width="15.875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="22.25" style="2" customWidth="1"/>
+    <col min="6" max="6" width="24.875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.625" style="2" customWidth="1"/>
     <col min="8" max="8" width="22.25" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="9" max="9" width="26.25" style="2" customWidth="1"/>
+    <col min="10" max="10" width="22.625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="32.125" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:8">
+    <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1072,75 +1102,104 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:8">
+    <row r="2" s="1" customFormat="1" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:8">
+    <row r="3" s="1" customFormat="1" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="2:8">
       <c r="B4" s="3">
-        <v>2001</v>
-      </c>
-      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="2">
         <v>1000</v>
       </c>
-      <c r="D4" s="2">
-        <v>1002</v>
-      </c>
-      <c r="E4" s="2"/>
+      <c r="E4" s="2">
+        <v>1001</v>
+      </c>
       <c r="G4" s="2">
-        <v>1002</v>
+        <v>0.2</v>
       </c>
       <c r="H4" s="2">
-        <v>1</v>
+        <v>1001</v>
       </c>
     </row>
   </sheetData>
